--- a/src/testData/testApp.xlsx
+++ b/src/testData/testApp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Javascript\Framework\src\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA6F199-5BA7-4120-BB83-56A1F389D75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E48AEB-FB34-404B-8151-25387D009585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginData" sheetId="1" r:id="rId1"/>
@@ -114,9 +114,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -154,15 +155,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +507,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79CDC8C9-DDAB-4A38-B038-8D9F7AA8B45C}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.26953125" customWidth="1"/>
@@ -559,12 +559,15 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/testData/testApp.xlsx
+++ b/src/testData/testApp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Javascript\Framework\src\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E48AEB-FB34-404B-8151-25387D009585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577DE20F-002A-4A44-9822-A389D83F44EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
